--- a/research/traditional_assets/database/data/norway/norway_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_retail_automotive.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-7.3046875</v>
+        <v>-6.122448979591837</v>
       </c>
       <c r="H2">
-        <v>-7.3046875</v>
+        <v>-6.122448979591837</v>
       </c>
       <c r="I2">
-        <v>-9.4921875</v>
+        <v>-6.598639455782314</v>
       </c>
       <c r="J2">
-        <v>-9.4921875</v>
+        <v>-6.598639455782314</v>
       </c>
       <c r="K2">
-        <v>-2.47</v>
+        <v>-2.92</v>
       </c>
       <c r="L2">
-        <v>-9.6484375</v>
+        <v>-6.621315192743764</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,52 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
       <c r="V2">
-        <v>0.2959183673469387</v>
+        <v>0.7272727272727272</v>
+      </c>
+      <c r="W2">
+        <v>-0.7070217917675545</v>
       </c>
       <c r="X2">
-        <v>0.08161615424705736</v>
+        <v>0.07158739964967781</v>
+      </c>
+      <c r="Y2">
+        <v>-0.7786091914172324</v>
+      </c>
+      <c r="Z2">
+        <v>0.2085106382978724</v>
+      </c>
+      <c r="AA2">
+        <v>-1.375886524822695</v>
       </c>
       <c r="AB2">
-        <v>0.08155738009233651</v>
+        <v>0.07147928849152681</v>
+      </c>
+      <c r="AC2">
+        <v>-1.447365813314222</v>
       </c>
       <c r="AD2">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="AG2">
-        <v>-2.015</v>
+        <v>-2.786</v>
       </c>
       <c r="AH2">
-        <v>0.002181818181818182</v>
+        <v>0.003623188405797101</v>
       </c>
       <c r="AI2">
-        <v>0.003618817852834741</v>
+        <v>0.003759398496240602</v>
       </c>
       <c r="AJ2">
-        <v>-0.415892672858617</v>
+        <v>-2.618421052631579</v>
       </c>
       <c r="AK2">
-        <v>-0.9527186761229312</v>
+        <v>-3.015151515151516</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="AN2">
-        <v>-0.006493506493506493</v>
+        <v>-0.005109489051094891</v>
+      </c>
+      <c r="AO2">
+        <v>-85.58823529411765</v>
       </c>
       <c r="AP2">
-        <v>0.8722943722943721</v>
+        <v>1.016788321167883</v>
+      </c>
+      <c r="AQ2">
+        <v>111.9230769230769</v>
       </c>
     </row>
     <row r="3">
@@ -692,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-7.3046875</v>
+        <v>-6.122448979591837</v>
       </c>
       <c r="H3">
-        <v>-7.3046875</v>
+        <v>-6.122448979591837</v>
       </c>
       <c r="I3">
-        <v>-9.4921875</v>
+        <v>-6.598639455782314</v>
       </c>
       <c r="J3">
-        <v>-9.4921875</v>
+        <v>-6.598639455782314</v>
       </c>
       <c r="K3">
-        <v>-2.47</v>
+        <v>-2.92</v>
       </c>
       <c r="L3">
-        <v>-9.6484375</v>
+        <v>-6.621315192743764</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -731,52 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
       <c r="V3">
-        <v>0.2959183673469387</v>
+        <v>0.7272727272727272</v>
+      </c>
+      <c r="W3">
+        <v>-0.7070217917675545</v>
       </c>
       <c r="X3">
-        <v>0.08161615424705736</v>
+        <v>0.07158739964967781</v>
+      </c>
+      <c r="Y3">
+        <v>-0.7786091914172324</v>
+      </c>
+      <c r="Z3">
+        <v>0.2085106382978724</v>
+      </c>
+      <c r="AA3">
+        <v>-1.375886524822695</v>
       </c>
       <c r="AB3">
-        <v>0.08155738009233651</v>
+        <v>0.07147928849152681</v>
+      </c>
+      <c r="AC3">
+        <v>-1.447365813314222</v>
       </c>
       <c r="AD3">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="AG3">
-        <v>-2.015</v>
+        <v>-2.786</v>
       </c>
       <c r="AH3">
-        <v>0.002181818181818182</v>
+        <v>0.003623188405797101</v>
       </c>
       <c r="AI3">
-        <v>0.003618817852834741</v>
+        <v>0.003759398496240602</v>
       </c>
       <c r="AJ3">
-        <v>-0.415892672858617</v>
+        <v>-2.618421052631579</v>
       </c>
       <c r="AK3">
-        <v>-0.9527186761229312</v>
+        <v>-3.015151515151516</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="AN3">
-        <v>-0.006493506493506493</v>
+        <v>-0.005109489051094891</v>
+      </c>
+      <c r="AO3">
+        <v>-85.58823529411765</v>
       </c>
       <c r="AP3">
-        <v>0.8722943722943721</v>
+        <v>1.016788321167883</v>
+      </c>
+      <c r="AQ3">
+        <v>111.9230769230769</v>
       </c>
     </row>
   </sheetData>
